--- a/assets/report_templates/TUPAD_Report_Blank.xlsx
+++ b/assets/report_templates/TUPAD_Report_Blank.xlsx
@@ -349,34 +349,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="146">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -384,12 +392,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -400,7 +410,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -415,19 +425,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -436,20 +446,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -461,16 +473,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -479,19 +491,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -500,37 +512,37 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -539,22 +551,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -569,10 +581,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -581,16 +593,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -611,16 +623,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -638,7 +650,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -647,10 +659,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -658,15 +670,17 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -675,30 +689,34 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -710,10 +728,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -722,41 +740,53 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -800,7 +830,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6600000" cy="750000"/>
+    <xdr:ext cx="11430000" cy="1298864"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="PESO Vinzons letterhead"/>
@@ -1024,30 +1054,40 @@
   <dimension ref="A1:AF1010"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" customWidth="1"/>
-    <col min="6" max="7" width="22.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" customWidth="1"/>
-    <col min="11" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="17.140625" customWidth="1"/>
-    <col min="15" max="15" width="22.5703125" style="107" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" customWidth="1"/>
-    <col min="17" max="17" width="8.42578125" customWidth="1"/>
-    <col min="18" max="18" width="17.7109375" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" customWidth="1"/>
-    <col min="20" max="20" width="7.42578125" customWidth="1"/>
-    <col min="21" max="21" width="7.5703125" customWidth="1"/>
-    <col min="23" max="23" width="26.28515625" customWidth="1"/>
-    <col min="24" max="24" width="26.85546875" customWidth="1"/>
-    <col min="27" max="27" width="38.5703125" customWidth="1"/>
-    <col min="28" max="28" width="47.28515625" style="94" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1" hidden="1"/>
+    <col min="7" max="7" width="18" customWidth="1" hidden="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="8" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
+    <col min="24" max="24" width="22" customWidth="1"/>
+    <col min="25" max="25" width="30" customWidth="1"/>
+    <col min="26" max="26" width="22" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="18" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="64" customHeight="1">
+    <row r="1" spans="1:31" ht="110" customHeight="1">
       <c r="A1" s="136"/>
       <c r="B1" s="137"/>
       <c r="C1" s="137"/>
@@ -1354,7 +1394,7 @@
       <c r="AD9" s="14"/>
       <c r="AE9" s="14"/>
     </row>
-    <row r="10" spans="1:31" ht="123.75" customHeight="1">
+    <row r="10" spans="1:31" ht="72" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>No.</t>
@@ -36498,12 +36538,21 @@
       <c r="AE1010" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="14">
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="U4:Y4"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="I9:M9"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:AB3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:AB4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:AB5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:AB6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:AB7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="10000" scale="19" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>

--- a/assets/report_templates/TUPAD_Report_Blank.xlsx
+++ b/assets/report_templates/TUPAD_Report_Blank.xlsx
@@ -1131,10 +1131,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>690563</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="13906500" cy="1580300"/>
     <xdr:pic>

--- a/assets/report_templates/TUPAD_Report_Blank.xlsx
+++ b/assets/report_templates/TUPAD_Report_Blank.xlsx
@@ -1131,8 +1131,8 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>690563</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
